--- a/display/Col_Cards_Totals_v1.xlsx
+++ b/display/Col_Cards_Totals_v1.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O640"/>
+  <dimension ref="A1:O651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -14627,7 +14627,7 @@
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>NOTES</t>
+          <t>ALBUM COMPLETION (population-weighted)</t>
         </is>
       </c>
       <c r="B258" s="6" t="n"/>
@@ -14637,947 +14637,628 @@
       <c r="F258" s="6" t="n"/>
       <c r="G258" s="6" t="n"/>
       <c r="H258" s="6" t="n"/>
+      <c r="I258" s="6" t="n"/>
+      <c r="J258" s="6" t="n"/>
+      <c r="K258" s="6" t="n"/>
+      <c r="L258" s="6" t="n"/>
     </row>
     <row r="259">
-      <c r="A259" s="4" t="inlineStr">
+      <c r="A259" s="7" t="n"/>
+      <c r="B259" s="7" t="n"/>
+      <c r="C259" s="7" t="n"/>
+      <c r="D259" s="7" t="n"/>
+      <c r="E259" s="7" t="n"/>
+      <c r="F259" s="7" t="n"/>
+      <c r="G259" s="7" t="n"/>
+      <c r="H259" s="7" t="n"/>
+      <c r="I259" s="7" t="n"/>
+      <c r="J259" s="7" t="n"/>
+      <c r="K259" s="7" t="n"/>
+      <c r="L259" s="7" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L260" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L261" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L262" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L263" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L267" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="n"/>
+      <c r="C269" s="6" t="n"/>
+      <c r="D269" s="6" t="n"/>
+      <c r="E269" s="6" t="n"/>
+      <c r="F269" s="6" t="n"/>
+      <c r="G269" s="6" t="n"/>
+      <c r="H269" s="6" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
         <is>
           <t>Ranges are p10-p90 ACROSS PLAYERS, not min-max: with 50 players the true extremes are single outliers that move every run.</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
         <is>
           <t>CADENCE gives three per-day rates because "packs per day" has three denominators: all 33 calendar days (comparable across segments, carries attendance in it), the days the player actually played (the pacing number), and the days that dropped anything (what the Col_Cards_Daily log reads like, because packs clump). Both denominators are on the sheet, so each rate x its day count = Total Packs Opened, above.</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="4" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
         <is>
           <t>ECONOMY IMPACT is what the collection feature PAYS OUT (SET + ALBUM REWARDS). It is not the segment's whole economy.</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="4" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
         <is>
           <t>A zero in a per-source row is a finding, not a gap — e.g. Kite Festival at its assumed 0.35 opt-in, or a ladder with no pack authored on it.</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="4" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
         <is>
           <t>"A. 0" is absent by design: data_seg_beh has no row for it, so nothing can price its reach.</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="4" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
         <is>
           <t>Envelopes are priced off the _v2 ladders ONLY, in the 1-star Dly .. 6-star Dly columns. A pack typed on a base sheet, or under any other column heading, moves nothing here. On a LEADERBOARD the top rows are ranks 1-3, which a mid segment reaches ~5% of the time: a pack put there is worth ~0.006 packs a season.</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="4" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
         <is>
           <t>PACK &amp; CARD MIX, one table per engagement level and payer flag, is BELOW this block. It breaks each source down by pack tier and card rarity; every row adds up to that source PACKS PER SOURCE and CARDS PER SOURCE figures above.</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="4" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
         <is>
           <t>The MAX column is a CEILING, not a cohort and not a forecast: 40-99 PAYER data with attendance, opt-in, every finishing rank and every milestone forced to their best, and the whole Season Pass track owned. Nobody plays like that. Its range is still p10-p90 because the card DRAWS stay random - that spread is how the cards fell, nothing else.</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="5" t="inlineStr">
+    <row r="279">
+      <c r="A279" s="5" t="inlineStr">
         <is>
           <t>PACK &amp; CARD MIX - 0-9 NONPAYER</t>
         </is>
       </c>
-      <c r="B268" s="6" t="n"/>
-      <c r="C268" s="6" t="n"/>
-      <c r="D268" s="6" t="n"/>
-      <c r="E268" s="6" t="n"/>
-      <c r="F268" s="6" t="n"/>
-      <c r="G268" s="6" t="n"/>
-      <c r="H268" s="6" t="n"/>
-      <c r="I268" s="6" t="n"/>
-      <c r="J268" s="6" t="n"/>
-      <c r="K268" s="6" t="n"/>
-      <c r="L268" s="6" t="n"/>
-      <c r="M268" s="6" t="n"/>
-      <c r="N268" s="6" t="n"/>
-      <c r="O268" s="6" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="7" t="n"/>
-      <c r="B269" s="7" t="n"/>
-      <c r="C269" s="7" t="n"/>
-      <c r="D269" s="7" t="n"/>
-      <c r="E269" s="7" t="n"/>
-      <c r="F269" s="7" t="n"/>
-      <c r="G269" s="7" t="n"/>
-      <c r="H269" s="7" t="n"/>
-      <c r="I269" s="7" t="n"/>
-      <c r="J269" s="7" t="n"/>
-      <c r="K269" s="7" t="n"/>
-      <c r="L269" s="7" t="n"/>
-      <c r="M269" s="7" t="n"/>
-      <c r="N269" s="7" t="n"/>
-      <c r="O269" s="7" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O270" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O271" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O272" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O273" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O274" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O275" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O276" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O277" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O278" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O279" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B279" s="6" t="n"/>
+      <c r="C279" s="6" t="n"/>
+      <c r="D279" s="6" t="n"/>
+      <c r="E279" s="6" t="n"/>
+      <c r="F279" s="6" t="n"/>
+      <c r="G279" s="6" t="n"/>
+      <c r="H279" s="6" t="n"/>
+      <c r="I279" s="6" t="n"/>
+      <c r="J279" s="6" t="n"/>
+      <c r="K279" s="6" t="n"/>
+      <c r="L279" s="6" t="n"/>
+      <c r="M279" s="6" t="n"/>
+      <c r="N279" s="6" t="n"/>
+      <c r="O279" s="6" t="n"/>
     </row>
     <row r="280">
-      <c r="A280" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O280" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A280" s="7" t="n"/>
+      <c r="B280" s="7" t="n"/>
+      <c r="C280" s="7" t="n"/>
+      <c r="D280" s="7" t="n"/>
+      <c r="E280" s="7" t="n"/>
+      <c r="F280" s="7" t="n"/>
+      <c r="G280" s="7" t="n"/>
+      <c r="H280" s="7" t="n"/>
+      <c r="I280" s="7" t="n"/>
+      <c r="J280" s="7" t="n"/>
+      <c r="K280" s="7" t="n"/>
+      <c r="L280" s="7" t="n"/>
+      <c r="M280" s="7" t="n"/>
+      <c r="N280" s="7" t="n"/>
+      <c r="O280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="8" t="inlineStr">
@@ -17119,43 +16800,236 @@
         </is>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O301" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="302">
-      <c r="A302" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - 0-9 PAYER</t>
-        </is>
-      </c>
-      <c r="B302" s="6" t="n"/>
-      <c r="C302" s="6" t="n"/>
-      <c r="D302" s="6" t="n"/>
-      <c r="E302" s="6" t="n"/>
-      <c r="F302" s="6" t="n"/>
-      <c r="G302" s="6" t="n"/>
-      <c r="H302" s="6" t="n"/>
-      <c r="I302" s="6" t="n"/>
-      <c r="J302" s="6" t="n"/>
-      <c r="K302" s="6" t="n"/>
-      <c r="L302" s="6" t="n"/>
-      <c r="M302" s="6" t="n"/>
-      <c r="N302" s="6" t="n"/>
-      <c r="O302" s="6" t="n"/>
+      <c r="A302" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O302" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="303">
-      <c r="A303" s="7" t="n"/>
-      <c r="B303" s="7" t="n"/>
-      <c r="C303" s="7" t="n"/>
-      <c r="D303" s="7" t="n"/>
-      <c r="E303" s="7" t="n"/>
-      <c r="F303" s="7" t="n"/>
-      <c r="G303" s="7" t="n"/>
-      <c r="H303" s="7" t="n"/>
-      <c r="I303" s="7" t="n"/>
-      <c r="J303" s="7" t="n"/>
-      <c r="K303" s="7" t="n"/>
-      <c r="L303" s="7" t="n"/>
-      <c r="M303" s="7" t="n"/>
-      <c r="N303" s="7" t="n"/>
-      <c r="O303" s="7" t="n"/>
+      <c r="A303" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O303" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="8" t="inlineStr">
@@ -17773,236 +17647,43 @@
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O312" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="313">
-      <c r="A313" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O313" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - 0-9 PAYER</t>
+        </is>
+      </c>
+      <c r="B313" s="6" t="n"/>
+      <c r="C313" s="6" t="n"/>
+      <c r="D313" s="6" t="n"/>
+      <c r="E313" s="6" t="n"/>
+      <c r="F313" s="6" t="n"/>
+      <c r="G313" s="6" t="n"/>
+      <c r="H313" s="6" t="n"/>
+      <c r="I313" s="6" t="n"/>
+      <c r="J313" s="6" t="n"/>
+      <c r="K313" s="6" t="n"/>
+      <c r="L313" s="6" t="n"/>
+      <c r="M313" s="6" t="n"/>
+      <c r="N313" s="6" t="n"/>
+      <c r="O313" s="6" t="n"/>
     </row>
     <row r="314">
-      <c r="A314" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O314" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A314" s="7" t="n"/>
+      <c r="B314" s="7" t="n"/>
+      <c r="C314" s="7" t="n"/>
+      <c r="D314" s="7" t="n"/>
+      <c r="E314" s="7" t="n"/>
+      <c r="F314" s="7" t="n"/>
+      <c r="G314" s="7" t="n"/>
+      <c r="H314" s="7" t="n"/>
+      <c r="I314" s="7" t="n"/>
+      <c r="J314" s="7" t="n"/>
+      <c r="K314" s="7" t="n"/>
+      <c r="L314" s="7" t="n"/>
+      <c r="M314" s="7" t="n"/>
+      <c r="N314" s="7" t="n"/>
+      <c r="O314" s="7" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="8" t="inlineStr">
@@ -19544,43 +19225,236 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O335" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="336">
-      <c r="A336" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - 10-19 NONPAYER</t>
-        </is>
-      </c>
-      <c r="B336" s="6" t="n"/>
-      <c r="C336" s="6" t="n"/>
-      <c r="D336" s="6" t="n"/>
-      <c r="E336" s="6" t="n"/>
-      <c r="F336" s="6" t="n"/>
-      <c r="G336" s="6" t="n"/>
-      <c r="H336" s="6" t="n"/>
-      <c r="I336" s="6" t="n"/>
-      <c r="J336" s="6" t="n"/>
-      <c r="K336" s="6" t="n"/>
-      <c r="L336" s="6" t="n"/>
-      <c r="M336" s="6" t="n"/>
-      <c r="N336" s="6" t="n"/>
-      <c r="O336" s="6" t="n"/>
+      <c r="A336" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O336" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="337">
-      <c r="A337" s="7" t="n"/>
-      <c r="B337" s="7" t="n"/>
-      <c r="C337" s="7" t="n"/>
-      <c r="D337" s="7" t="n"/>
-      <c r="E337" s="7" t="n"/>
-      <c r="F337" s="7" t="n"/>
-      <c r="G337" s="7" t="n"/>
-      <c r="H337" s="7" t="n"/>
-      <c r="I337" s="7" t="n"/>
-      <c r="J337" s="7" t="n"/>
-      <c r="K337" s="7" t="n"/>
-      <c r="L337" s="7" t="n"/>
-      <c r="M337" s="7" t="n"/>
-      <c r="N337" s="7" t="n"/>
-      <c r="O337" s="7" t="n"/>
+      <c r="A337" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O337" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="8" t="inlineStr">
@@ -20198,236 +20072,43 @@
         </is>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O346" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="347">
-      <c r="A347" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O347" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A347" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - 10-19 NONPAYER</t>
+        </is>
+      </c>
+      <c r="B347" s="6" t="n"/>
+      <c r="C347" s="6" t="n"/>
+      <c r="D347" s="6" t="n"/>
+      <c r="E347" s="6" t="n"/>
+      <c r="F347" s="6" t="n"/>
+      <c r="G347" s="6" t="n"/>
+      <c r="H347" s="6" t="n"/>
+      <c r="I347" s="6" t="n"/>
+      <c r="J347" s="6" t="n"/>
+      <c r="K347" s="6" t="n"/>
+      <c r="L347" s="6" t="n"/>
+      <c r="M347" s="6" t="n"/>
+      <c r="N347" s="6" t="n"/>
+      <c r="O347" s="6" t="n"/>
     </row>
     <row r="348">
-      <c r="A348" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O348" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A348" s="7" t="n"/>
+      <c r="B348" s="7" t="n"/>
+      <c r="C348" s="7" t="n"/>
+      <c r="D348" s="7" t="n"/>
+      <c r="E348" s="7" t="n"/>
+      <c r="F348" s="7" t="n"/>
+      <c r="G348" s="7" t="n"/>
+      <c r="H348" s="7" t="n"/>
+      <c r="I348" s="7" t="n"/>
+      <c r="J348" s="7" t="n"/>
+      <c r="K348" s="7" t="n"/>
+      <c r="L348" s="7" t="n"/>
+      <c r="M348" s="7" t="n"/>
+      <c r="N348" s="7" t="n"/>
+      <c r="O348" s="7" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="8" t="inlineStr">
@@ -21969,43 +21650,236 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O369" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="370">
-      <c r="A370" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - 10-19 PAYER</t>
-        </is>
-      </c>
-      <c r="B370" s="6" t="n"/>
-      <c r="C370" s="6" t="n"/>
-      <c r="D370" s="6" t="n"/>
-      <c r="E370" s="6" t="n"/>
-      <c r="F370" s="6" t="n"/>
-      <c r="G370" s="6" t="n"/>
-      <c r="H370" s="6" t="n"/>
-      <c r="I370" s="6" t="n"/>
-      <c r="J370" s="6" t="n"/>
-      <c r="K370" s="6" t="n"/>
-      <c r="L370" s="6" t="n"/>
-      <c r="M370" s="6" t="n"/>
-      <c r="N370" s="6" t="n"/>
-      <c r="O370" s="6" t="n"/>
+      <c r="A370" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O370" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="371">
-      <c r="A371" s="7" t="n"/>
-      <c r="B371" s="7" t="n"/>
-      <c r="C371" s="7" t="n"/>
-      <c r="D371" s="7" t="n"/>
-      <c r="E371" s="7" t="n"/>
-      <c r="F371" s="7" t="n"/>
-      <c r="G371" s="7" t="n"/>
-      <c r="H371" s="7" t="n"/>
-      <c r="I371" s="7" t="n"/>
-      <c r="J371" s="7" t="n"/>
-      <c r="K371" s="7" t="n"/>
-      <c r="L371" s="7" t="n"/>
-      <c r="M371" s="7" t="n"/>
-      <c r="N371" s="7" t="n"/>
-      <c r="O371" s="7" t="n"/>
+      <c r="A371" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O371" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="8" t="inlineStr">
@@ -22623,236 +22497,43 @@
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O380" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="381">
-      <c r="A381" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O381" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A381" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - 10-19 PAYER</t>
+        </is>
+      </c>
+      <c r="B381" s="6" t="n"/>
+      <c r="C381" s="6" t="n"/>
+      <c r="D381" s="6" t="n"/>
+      <c r="E381" s="6" t="n"/>
+      <c r="F381" s="6" t="n"/>
+      <c r="G381" s="6" t="n"/>
+      <c r="H381" s="6" t="n"/>
+      <c r="I381" s="6" t="n"/>
+      <c r="J381" s="6" t="n"/>
+      <c r="K381" s="6" t="n"/>
+      <c r="L381" s="6" t="n"/>
+      <c r="M381" s="6" t="n"/>
+      <c r="N381" s="6" t="n"/>
+      <c r="O381" s="6" t="n"/>
     </row>
     <row r="382">
-      <c r="A382" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O382" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A382" s="7" t="n"/>
+      <c r="B382" s="7" t="n"/>
+      <c r="C382" s="7" t="n"/>
+      <c r="D382" s="7" t="n"/>
+      <c r="E382" s="7" t="n"/>
+      <c r="F382" s="7" t="n"/>
+      <c r="G382" s="7" t="n"/>
+      <c r="H382" s="7" t="n"/>
+      <c r="I382" s="7" t="n"/>
+      <c r="J382" s="7" t="n"/>
+      <c r="K382" s="7" t="n"/>
+      <c r="L382" s="7" t="n"/>
+      <c r="M382" s="7" t="n"/>
+      <c r="N382" s="7" t="n"/>
+      <c r="O382" s="7" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="8" t="inlineStr">
@@ -24394,43 +24075,236 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O403" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="404">
-      <c r="A404" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - 20-39 NONPAYER</t>
-        </is>
-      </c>
-      <c r="B404" s="6" t="n"/>
-      <c r="C404" s="6" t="n"/>
-      <c r="D404" s="6" t="n"/>
-      <c r="E404" s="6" t="n"/>
-      <c r="F404" s="6" t="n"/>
-      <c r="G404" s="6" t="n"/>
-      <c r="H404" s="6" t="n"/>
-      <c r="I404" s="6" t="n"/>
-      <c r="J404" s="6" t="n"/>
-      <c r="K404" s="6" t="n"/>
-      <c r="L404" s="6" t="n"/>
-      <c r="M404" s="6" t="n"/>
-      <c r="N404" s="6" t="n"/>
-      <c r="O404" s="6" t="n"/>
+      <c r="A404" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O404" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="405">
-      <c r="A405" s="7" t="n"/>
-      <c r="B405" s="7" t="n"/>
-      <c r="C405" s="7" t="n"/>
-      <c r="D405" s="7" t="n"/>
-      <c r="E405" s="7" t="n"/>
-      <c r="F405" s="7" t="n"/>
-      <c r="G405" s="7" t="n"/>
-      <c r="H405" s="7" t="n"/>
-      <c r="I405" s="7" t="n"/>
-      <c r="J405" s="7" t="n"/>
-      <c r="K405" s="7" t="n"/>
-      <c r="L405" s="7" t="n"/>
-      <c r="M405" s="7" t="n"/>
-      <c r="N405" s="7" t="n"/>
-      <c r="O405" s="7" t="n"/>
+      <c r="A405" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O405" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="8" t="inlineStr">
@@ -25048,236 +24922,43 @@
         </is>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O414" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="415">
-      <c r="A415" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O415" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A415" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - 20-39 NONPAYER</t>
+        </is>
+      </c>
+      <c r="B415" s="6" t="n"/>
+      <c r="C415" s="6" t="n"/>
+      <c r="D415" s="6" t="n"/>
+      <c r="E415" s="6" t="n"/>
+      <c r="F415" s="6" t="n"/>
+      <c r="G415" s="6" t="n"/>
+      <c r="H415" s="6" t="n"/>
+      <c r="I415" s="6" t="n"/>
+      <c r="J415" s="6" t="n"/>
+      <c r="K415" s="6" t="n"/>
+      <c r="L415" s="6" t="n"/>
+      <c r="M415" s="6" t="n"/>
+      <c r="N415" s="6" t="n"/>
+      <c r="O415" s="6" t="n"/>
     </row>
     <row r="416">
-      <c r="A416" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O416" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A416" s="7" t="n"/>
+      <c r="B416" s="7" t="n"/>
+      <c r="C416" s="7" t="n"/>
+      <c r="D416" s="7" t="n"/>
+      <c r="E416" s="7" t="n"/>
+      <c r="F416" s="7" t="n"/>
+      <c r="G416" s="7" t="n"/>
+      <c r="H416" s="7" t="n"/>
+      <c r="I416" s="7" t="n"/>
+      <c r="J416" s="7" t="n"/>
+      <c r="K416" s="7" t="n"/>
+      <c r="L416" s="7" t="n"/>
+      <c r="M416" s="7" t="n"/>
+      <c r="N416" s="7" t="n"/>
+      <c r="O416" s="7" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="8" t="inlineStr">
@@ -26819,43 +26500,236 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O437" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="438">
-      <c r="A438" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - 20-39 PAYER</t>
-        </is>
-      </c>
-      <c r="B438" s="6" t="n"/>
-      <c r="C438" s="6" t="n"/>
-      <c r="D438" s="6" t="n"/>
-      <c r="E438" s="6" t="n"/>
-      <c r="F438" s="6" t="n"/>
-      <c r="G438" s="6" t="n"/>
-      <c r="H438" s="6" t="n"/>
-      <c r="I438" s="6" t="n"/>
-      <c r="J438" s="6" t="n"/>
-      <c r="K438" s="6" t="n"/>
-      <c r="L438" s="6" t="n"/>
-      <c r="M438" s="6" t="n"/>
-      <c r="N438" s="6" t="n"/>
-      <c r="O438" s="6" t="n"/>
+      <c r="A438" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O438" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="439">
-      <c r="A439" s="7" t="n"/>
-      <c r="B439" s="7" t="n"/>
-      <c r="C439" s="7" t="n"/>
-      <c r="D439" s="7" t="n"/>
-      <c r="E439" s="7" t="n"/>
-      <c r="F439" s="7" t="n"/>
-      <c r="G439" s="7" t="n"/>
-      <c r="H439" s="7" t="n"/>
-      <c r="I439" s="7" t="n"/>
-      <c r="J439" s="7" t="n"/>
-      <c r="K439" s="7" t="n"/>
-      <c r="L439" s="7" t="n"/>
-      <c r="M439" s="7" t="n"/>
-      <c r="N439" s="7" t="n"/>
-      <c r="O439" s="7" t="n"/>
+      <c r="A439" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O439" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="8" t="inlineStr">
@@ -27473,236 +27347,43 @@
         </is>
       </c>
     </row>
-    <row r="448">
-      <c r="A448" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O448" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="449">
-      <c r="A449" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O449" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A449" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - 20-39 PAYER</t>
+        </is>
+      </c>
+      <c r="B449" s="6" t="n"/>
+      <c r="C449" s="6" t="n"/>
+      <c r="D449" s="6" t="n"/>
+      <c r="E449" s="6" t="n"/>
+      <c r="F449" s="6" t="n"/>
+      <c r="G449" s="6" t="n"/>
+      <c r="H449" s="6" t="n"/>
+      <c r="I449" s="6" t="n"/>
+      <c r="J449" s="6" t="n"/>
+      <c r="K449" s="6" t="n"/>
+      <c r="L449" s="6" t="n"/>
+      <c r="M449" s="6" t="n"/>
+      <c r="N449" s="6" t="n"/>
+      <c r="O449" s="6" t="n"/>
     </row>
     <row r="450">
-      <c r="A450" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O450" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A450" s="7" t="n"/>
+      <c r="B450" s="7" t="n"/>
+      <c r="C450" s="7" t="n"/>
+      <c r="D450" s="7" t="n"/>
+      <c r="E450" s="7" t="n"/>
+      <c r="F450" s="7" t="n"/>
+      <c r="G450" s="7" t="n"/>
+      <c r="H450" s="7" t="n"/>
+      <c r="I450" s="7" t="n"/>
+      <c r="J450" s="7" t="n"/>
+      <c r="K450" s="7" t="n"/>
+      <c r="L450" s="7" t="n"/>
+      <c r="M450" s="7" t="n"/>
+      <c r="N450" s="7" t="n"/>
+      <c r="O450" s="7" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="8" t="inlineStr">
@@ -29244,43 +28925,236 @@
         </is>
       </c>
     </row>
+    <row r="471">
+      <c r="A471" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O471" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="472">
-      <c r="A472" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - 40-99 NONPAYER</t>
-        </is>
-      </c>
-      <c r="B472" s="6" t="n"/>
-      <c r="C472" s="6" t="n"/>
-      <c r="D472" s="6" t="n"/>
-      <c r="E472" s="6" t="n"/>
-      <c r="F472" s="6" t="n"/>
-      <c r="G472" s="6" t="n"/>
-      <c r="H472" s="6" t="n"/>
-      <c r="I472" s="6" t="n"/>
-      <c r="J472" s="6" t="n"/>
-      <c r="K472" s="6" t="n"/>
-      <c r="L472" s="6" t="n"/>
-      <c r="M472" s="6" t="n"/>
-      <c r="N472" s="6" t="n"/>
-      <c r="O472" s="6" t="n"/>
+      <c r="A472" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O472" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="473">
-      <c r="A473" s="7" t="n"/>
-      <c r="B473" s="7" t="n"/>
-      <c r="C473" s="7" t="n"/>
-      <c r="D473" s="7" t="n"/>
-      <c r="E473" s="7" t="n"/>
-      <c r="F473" s="7" t="n"/>
-      <c r="G473" s="7" t="n"/>
-      <c r="H473" s="7" t="n"/>
-      <c r="I473" s="7" t="n"/>
-      <c r="J473" s="7" t="n"/>
-      <c r="K473" s="7" t="n"/>
-      <c r="L473" s="7" t="n"/>
-      <c r="M473" s="7" t="n"/>
-      <c r="N473" s="7" t="n"/>
-      <c r="O473" s="7" t="n"/>
+      <c r="A473" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O473" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="8" t="inlineStr">
@@ -29898,236 +29772,43 @@
         </is>
       </c>
     </row>
-    <row r="482">
-      <c r="A482" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O482" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="483">
-      <c r="A483" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O483" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A483" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - 40-99 NONPAYER</t>
+        </is>
+      </c>
+      <c r="B483" s="6" t="n"/>
+      <c r="C483" s="6" t="n"/>
+      <c r="D483" s="6" t="n"/>
+      <c r="E483" s="6" t="n"/>
+      <c r="F483" s="6" t="n"/>
+      <c r="G483" s="6" t="n"/>
+      <c r="H483" s="6" t="n"/>
+      <c r="I483" s="6" t="n"/>
+      <c r="J483" s="6" t="n"/>
+      <c r="K483" s="6" t="n"/>
+      <c r="L483" s="6" t="n"/>
+      <c r="M483" s="6" t="n"/>
+      <c r="N483" s="6" t="n"/>
+      <c r="O483" s="6" t="n"/>
     </row>
     <row r="484">
-      <c r="A484" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O484" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A484" s="7" t="n"/>
+      <c r="B484" s="7" t="n"/>
+      <c r="C484" s="7" t="n"/>
+      <c r="D484" s="7" t="n"/>
+      <c r="E484" s="7" t="n"/>
+      <c r="F484" s="7" t="n"/>
+      <c r="G484" s="7" t="n"/>
+      <c r="H484" s="7" t="n"/>
+      <c r="I484" s="7" t="n"/>
+      <c r="J484" s="7" t="n"/>
+      <c r="K484" s="7" t="n"/>
+      <c r="L484" s="7" t="n"/>
+      <c r="M484" s="7" t="n"/>
+      <c r="N484" s="7" t="n"/>
+      <c r="O484" s="7" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="8" t="inlineStr">
@@ -31669,43 +31350,236 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O505" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="506">
-      <c r="A506" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - 40-99 PAYER</t>
-        </is>
-      </c>
-      <c r="B506" s="6" t="n"/>
-      <c r="C506" s="6" t="n"/>
-      <c r="D506" s="6" t="n"/>
-      <c r="E506" s="6" t="n"/>
-      <c r="F506" s="6" t="n"/>
-      <c r="G506" s="6" t="n"/>
-      <c r="H506" s="6" t="n"/>
-      <c r="I506" s="6" t="n"/>
-      <c r="J506" s="6" t="n"/>
-      <c r="K506" s="6" t="n"/>
-      <c r="L506" s="6" t="n"/>
-      <c r="M506" s="6" t="n"/>
-      <c r="N506" s="6" t="n"/>
-      <c r="O506" s="6" t="n"/>
+      <c r="A506" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O506" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="507">
-      <c r="A507" s="7" t="n"/>
-      <c r="B507" s="7" t="n"/>
-      <c r="C507" s="7" t="n"/>
-      <c r="D507" s="7" t="n"/>
-      <c r="E507" s="7" t="n"/>
-      <c r="F507" s="7" t="n"/>
-      <c r="G507" s="7" t="n"/>
-      <c r="H507" s="7" t="n"/>
-      <c r="I507" s="7" t="n"/>
-      <c r="J507" s="7" t="n"/>
-      <c r="K507" s="7" t="n"/>
-      <c r="L507" s="7" t="n"/>
-      <c r="M507" s="7" t="n"/>
-      <c r="N507" s="7" t="n"/>
-      <c r="O507" s="7" t="n"/>
+      <c r="A507" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O507" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="8" t="inlineStr">
@@ -32323,236 +32197,43 @@
         </is>
       </c>
     </row>
-    <row r="516">
-      <c r="A516" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O516" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="517">
-      <c r="A517" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O517" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A517" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - 40-99 PAYER</t>
+        </is>
+      </c>
+      <c r="B517" s="6" t="n"/>
+      <c r="C517" s="6" t="n"/>
+      <c r="D517" s="6" t="n"/>
+      <c r="E517" s="6" t="n"/>
+      <c r="F517" s="6" t="n"/>
+      <c r="G517" s="6" t="n"/>
+      <c r="H517" s="6" t="n"/>
+      <c r="I517" s="6" t="n"/>
+      <c r="J517" s="6" t="n"/>
+      <c r="K517" s="6" t="n"/>
+      <c r="L517" s="6" t="n"/>
+      <c r="M517" s="6" t="n"/>
+      <c r="N517" s="6" t="n"/>
+      <c r="O517" s="6" t="n"/>
     </row>
     <row r="518">
-      <c r="A518" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O518" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A518" s="7" t="n"/>
+      <c r="B518" s="7" t="n"/>
+      <c r="C518" s="7" t="n"/>
+      <c r="D518" s="7" t="n"/>
+      <c r="E518" s="7" t="n"/>
+      <c r="F518" s="7" t="n"/>
+      <c r="G518" s="7" t="n"/>
+      <c r="H518" s="7" t="n"/>
+      <c r="I518" s="7" t="n"/>
+      <c r="J518" s="7" t="n"/>
+      <c r="K518" s="7" t="n"/>
+      <c r="L518" s="7" t="n"/>
+      <c r="M518" s="7" t="n"/>
+      <c r="N518" s="7" t="n"/>
+      <c r="O518" s="7" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="8" t="inlineStr">
@@ -34094,43 +33775,236 @@
         </is>
       </c>
     </row>
+    <row r="539">
+      <c r="A539" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O539" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="540">
-      <c r="A540" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - 100+ NONPAYER</t>
-        </is>
-      </c>
-      <c r="B540" s="6" t="n"/>
-      <c r="C540" s="6" t="n"/>
-      <c r="D540" s="6" t="n"/>
-      <c r="E540" s="6" t="n"/>
-      <c r="F540" s="6" t="n"/>
-      <c r="G540" s="6" t="n"/>
-      <c r="H540" s="6" t="n"/>
-      <c r="I540" s="6" t="n"/>
-      <c r="J540" s="6" t="n"/>
-      <c r="K540" s="6" t="n"/>
-      <c r="L540" s="6" t="n"/>
-      <c r="M540" s="6" t="n"/>
-      <c r="N540" s="6" t="n"/>
-      <c r="O540" s="6" t="n"/>
+      <c r="A540" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O540" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="541">
-      <c r="A541" s="7" t="n"/>
-      <c r="B541" s="7" t="n"/>
-      <c r="C541" s="7" t="n"/>
-      <c r="D541" s="7" t="n"/>
-      <c r="E541" s="7" t="n"/>
-      <c r="F541" s="7" t="n"/>
-      <c r="G541" s="7" t="n"/>
-      <c r="H541" s="7" t="n"/>
-      <c r="I541" s="7" t="n"/>
-      <c r="J541" s="7" t="n"/>
-      <c r="K541" s="7" t="n"/>
-      <c r="L541" s="7" t="n"/>
-      <c r="M541" s="7" t="n"/>
-      <c r="N541" s="7" t="n"/>
-      <c r="O541" s="7" t="n"/>
+      <c r="A541" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O541" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="8" t="inlineStr">
@@ -34748,236 +34622,43 @@
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O550" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="551">
-      <c r="A551" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O551" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A551" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - 100+ NONPAYER</t>
+        </is>
+      </c>
+      <c r="B551" s="6" t="n"/>
+      <c r="C551" s="6" t="n"/>
+      <c r="D551" s="6" t="n"/>
+      <c r="E551" s="6" t="n"/>
+      <c r="F551" s="6" t="n"/>
+      <c r="G551" s="6" t="n"/>
+      <c r="H551" s="6" t="n"/>
+      <c r="I551" s="6" t="n"/>
+      <c r="J551" s="6" t="n"/>
+      <c r="K551" s="6" t="n"/>
+      <c r="L551" s="6" t="n"/>
+      <c r="M551" s="6" t="n"/>
+      <c r="N551" s="6" t="n"/>
+      <c r="O551" s="6" t="n"/>
     </row>
     <row r="552">
-      <c r="A552" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O552" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A552" s="7" t="n"/>
+      <c r="B552" s="7" t="n"/>
+      <c r="C552" s="7" t="n"/>
+      <c r="D552" s="7" t="n"/>
+      <c r="E552" s="7" t="n"/>
+      <c r="F552" s="7" t="n"/>
+      <c r="G552" s="7" t="n"/>
+      <c r="H552" s="7" t="n"/>
+      <c r="I552" s="7" t="n"/>
+      <c r="J552" s="7" t="n"/>
+      <c r="K552" s="7" t="n"/>
+      <c r="L552" s="7" t="n"/>
+      <c r="M552" s="7" t="n"/>
+      <c r="N552" s="7" t="n"/>
+      <c r="O552" s="7" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="8" t="inlineStr">
@@ -36519,43 +36200,236 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O573" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="574">
-      <c r="A574" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - 100+ PAYER</t>
-        </is>
-      </c>
-      <c r="B574" s="6" t="n"/>
-      <c r="C574" s="6" t="n"/>
-      <c r="D574" s="6" t="n"/>
-      <c r="E574" s="6" t="n"/>
-      <c r="F574" s="6" t="n"/>
-      <c r="G574" s="6" t="n"/>
-      <c r="H574" s="6" t="n"/>
-      <c r="I574" s="6" t="n"/>
-      <c r="J574" s="6" t="n"/>
-      <c r="K574" s="6" t="n"/>
-      <c r="L574" s="6" t="n"/>
-      <c r="M574" s="6" t="n"/>
-      <c r="N574" s="6" t="n"/>
-      <c r="O574" s="6" t="n"/>
+      <c r="A574" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O574" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="575">
-      <c r="A575" s="7" t="n"/>
-      <c r="B575" s="7" t="n"/>
-      <c r="C575" s="7" t="n"/>
-      <c r="D575" s="7" t="n"/>
-      <c r="E575" s="7" t="n"/>
-      <c r="F575" s="7" t="n"/>
-      <c r="G575" s="7" t="n"/>
-      <c r="H575" s="7" t="n"/>
-      <c r="I575" s="7" t="n"/>
-      <c r="J575" s="7" t="n"/>
-      <c r="K575" s="7" t="n"/>
-      <c r="L575" s="7" t="n"/>
-      <c r="M575" s="7" t="n"/>
-      <c r="N575" s="7" t="n"/>
-      <c r="O575" s="7" t="n"/>
+      <c r="A575" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O575" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="8" t="inlineStr">
@@ -37173,236 +37047,43 @@
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O584" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="585">
-      <c r="A585" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O585" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A585" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - 100+ PAYER</t>
+        </is>
+      </c>
+      <c r="B585" s="6" t="n"/>
+      <c r="C585" s="6" t="n"/>
+      <c r="D585" s="6" t="n"/>
+      <c r="E585" s="6" t="n"/>
+      <c r="F585" s="6" t="n"/>
+      <c r="G585" s="6" t="n"/>
+      <c r="H585" s="6" t="n"/>
+      <c r="I585" s="6" t="n"/>
+      <c r="J585" s="6" t="n"/>
+      <c r="K585" s="6" t="n"/>
+      <c r="L585" s="6" t="n"/>
+      <c r="M585" s="6" t="n"/>
+      <c r="N585" s="6" t="n"/>
+      <c r="O585" s="6" t="n"/>
     </row>
     <row r="586">
-      <c r="A586" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O586" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A586" s="7" t="n"/>
+      <c r="B586" s="7" t="n"/>
+      <c r="C586" s="7" t="n"/>
+      <c r="D586" s="7" t="n"/>
+      <c r="E586" s="7" t="n"/>
+      <c r="F586" s="7" t="n"/>
+      <c r="G586" s="7" t="n"/>
+      <c r="H586" s="7" t="n"/>
+      <c r="I586" s="7" t="n"/>
+      <c r="J586" s="7" t="n"/>
+      <c r="K586" s="7" t="n"/>
+      <c r="L586" s="7" t="n"/>
+      <c r="M586" s="7" t="n"/>
+      <c r="N586" s="7" t="n"/>
+      <c r="O586" s="7" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="8" t="inlineStr">
@@ -38944,43 +38625,236 @@
         </is>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O607" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="608">
-      <c r="A608" s="5" t="inlineStr">
-        <is>
-          <t>PACK &amp; CARD MIX - MAX</t>
-        </is>
-      </c>
-      <c r="B608" s="6" t="n"/>
-      <c r="C608" s="6" t="n"/>
-      <c r="D608" s="6" t="n"/>
-      <c r="E608" s="6" t="n"/>
-      <c r="F608" s="6" t="n"/>
-      <c r="G608" s="6" t="n"/>
-      <c r="H608" s="6" t="n"/>
-      <c r="I608" s="6" t="n"/>
-      <c r="J608" s="6" t="n"/>
-      <c r="K608" s="6" t="n"/>
-      <c r="L608" s="6" t="n"/>
-      <c r="M608" s="6" t="n"/>
-      <c r="N608" s="6" t="n"/>
-      <c r="O608" s="6" t="n"/>
+      <c r="A608" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O608" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="609">
-      <c r="A609" s="7" t="n"/>
-      <c r="B609" s="7" t="n"/>
-      <c r="C609" s="7" t="n"/>
-      <c r="D609" s="7" t="n"/>
-      <c r="E609" s="7" t="n"/>
-      <c r="F609" s="7" t="n"/>
-      <c r="G609" s="7" t="n"/>
-      <c r="H609" s="7" t="n"/>
-      <c r="I609" s="7" t="n"/>
-      <c r="J609" s="7" t="n"/>
-      <c r="K609" s="7" t="n"/>
-      <c r="L609" s="7" t="n"/>
-      <c r="M609" s="7" t="n"/>
-      <c r="N609" s="7" t="n"/>
-      <c r="O609" s="7" t="n"/>
+      <c r="A609" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O609" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="8" t="inlineStr">
@@ -39598,236 +39472,43 @@
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O618" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="619">
-      <c r="A619" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O619" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A619" s="5" t="inlineStr">
+        <is>
+          <t>PACK &amp; CARD MIX - MAX</t>
+        </is>
+      </c>
+      <c r="B619" s="6" t="n"/>
+      <c r="C619" s="6" t="n"/>
+      <c r="D619" s="6" t="n"/>
+      <c r="E619" s="6" t="n"/>
+      <c r="F619" s="6" t="n"/>
+      <c r="G619" s="6" t="n"/>
+      <c r="H619" s="6" t="n"/>
+      <c r="I619" s="6" t="n"/>
+      <c r="J619" s="6" t="n"/>
+      <c r="K619" s="6" t="n"/>
+      <c r="L619" s="6" t="n"/>
+      <c r="M619" s="6" t="n"/>
+      <c r="N619" s="6" t="n"/>
+      <c r="O619" s="6" t="n"/>
     </row>
     <row r="620">
-      <c r="A620" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O620" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A620" s="7" t="n"/>
+      <c r="B620" s="7" t="n"/>
+      <c r="C620" s="7" t="n"/>
+      <c r="D620" s="7" t="n"/>
+      <c r="E620" s="7" t="n"/>
+      <c r="F620" s="7" t="n"/>
+      <c r="G620" s="7" t="n"/>
+      <c r="H620" s="7" t="n"/>
+      <c r="I620" s="7" t="n"/>
+      <c r="J620" s="7" t="n"/>
+      <c r="K620" s="7" t="n"/>
+      <c r="L620" s="7" t="n"/>
+      <c r="M620" s="7" t="n"/>
+      <c r="N620" s="7" t="n"/>
+      <c r="O620" s="7" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="8" t="inlineStr">
@@ -41364,6 +41045,853 @@
         </is>
       </c>
       <c r="O640" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O641" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O642" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O643" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O644" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O645" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O646" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O647" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O648" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O649" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O650" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N651" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O651" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
